--- a/imports/rooting_interests.xlsx
+++ b/imports/rooting_interests.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <workbookPr/>
   <sheets>
-    <sheet state="visible" name="Rooting" sheetId="1" r:id="rId5"/>
+    <sheet state="visible" name="Rooting Revised" sheetId="1" r:id="rId5"/>
     <sheet state="hidden" name="Lists" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="Reference" sheetId="3" r:id="rId7"/>
   </sheets>
@@ -13,36 +13,81 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="99">
+  <si>
+    <t>Stat</t>
+  </si>
   <si>
     <t>What the importer accepts</t>
   </si>
   <si>
-    <t>Stat</t>
-  </si>
-  <si>
     <t>Direction</t>
   </si>
   <si>
     <t>Team</t>
   </si>
   <si>
+    <t>pass yds</t>
+  </si>
+  <si>
+    <t>over</t>
+  </si>
+  <si>
+    <t>ARI</t>
+  </si>
+  <si>
+    <t>pass TD</t>
+  </si>
+  <si>
+    <t>under</t>
+  </si>
+  <si>
     <t>Goal syntax</t>
   </si>
   <si>
+    <t>ATL</t>
+  </si>
+  <si>
+    <t>completions</t>
+  </si>
+  <si>
+    <t>at least</t>
+  </si>
+  <si>
+    <t>BAL</t>
+  </si>
+  <si>
+    <t>attempts</t>
+  </si>
+  <si>
     <t>over N</t>
   </si>
   <si>
+    <t>(none)</t>
+  </si>
+  <si>
+    <t>BUF</t>
+  </si>
+  <si>
     <t>strictly greater than N</t>
   </si>
   <si>
     <t>under N</t>
   </si>
   <si>
+    <t>interceptions</t>
+  </si>
+  <si>
+    <t>CAR</t>
+  </si>
+  <si>
     <t>N or fewer; only settles when the game ends</t>
   </si>
   <si>
-    <t>pass yds</t>
+    <t>rush yds</t>
+  </si>
+  <si>
+    <t>CHI</t>
   </si>
   <si>
     <t>at least N</t>
@@ -51,263 +96,227 @@
     <t>shorthand for over N-1</t>
   </si>
   <si>
+    <t>rush TD</t>
+  </si>
+  <si>
+    <t>CIN</t>
+  </si>
+  <si>
     <t>any TD</t>
   </si>
   <si>
+    <t>carries</t>
+  </si>
+  <si>
+    <t>CLE</t>
+  </si>
+  <si>
     <t>at least one touchdown; leave Direction and Target blank</t>
   </si>
   <si>
-    <t>over</t>
+    <t>rec</t>
+  </si>
+  <si>
+    <t>DAL</t>
   </si>
   <si>
     <t>win</t>
   </si>
   <si>
-    <t>ARI</t>
+    <t>rec yds</t>
   </si>
   <si>
     <t>team goal; leave Player, Direction and Target blank</t>
   </si>
   <si>
-    <t>pass TD</t>
+    <t>DEN</t>
+  </si>
+  <si>
+    <t>rec TD</t>
   </si>
   <si>
     <t>points over N</t>
   </si>
   <si>
-    <t>under</t>
+    <t>DET</t>
   </si>
   <si>
     <t>team scores more than N</t>
   </si>
   <si>
-    <t>ATL</t>
+    <t>targets</t>
+  </si>
+  <si>
+    <t>GB</t>
   </si>
   <si>
     <t>Player stats</t>
   </si>
   <si>
-    <t>completions</t>
-  </si>
-  <si>
-    <t>at least</t>
-  </si>
-  <si>
-    <t>BAL</t>
-  </si>
-  <si>
-    <t>attempts</t>
-  </si>
-  <si>
-    <t>(none)</t>
-  </si>
-  <si>
-    <t>BUF</t>
-  </si>
-  <si>
-    <t>interceptions</t>
-  </si>
-  <si>
-    <t>CAR</t>
-  </si>
-  <si>
-    <t>rush yds</t>
-  </si>
-  <si>
-    <t>CHI</t>
-  </si>
-  <si>
-    <t>rush TD</t>
-  </si>
-  <si>
-    <t>CIN</t>
-  </si>
-  <si>
-    <t>carries</t>
-  </si>
-  <si>
-    <t>CLE</t>
-  </si>
-  <si>
-    <t>rec</t>
-  </si>
-  <si>
-    <t>DAL</t>
-  </si>
-  <si>
-    <t>rec yds</t>
-  </si>
-  <si>
-    <t>DEN</t>
-  </si>
-  <si>
-    <t>rec TD</t>
-  </si>
-  <si>
-    <t>DET</t>
-  </si>
-  <si>
-    <t>targets</t>
-  </si>
-  <si>
-    <t>GB</t>
+    <t>HOU</t>
   </si>
   <si>
     <t>tackles</t>
   </si>
   <si>
-    <t>HOU</t>
+    <t>IND</t>
   </si>
   <si>
     <t>solo tackles</t>
   </si>
   <si>
-    <t>IND</t>
+    <t>JAX</t>
   </si>
   <si>
     <t>sacks</t>
   </si>
   <si>
-    <t>JAX</t>
+    <t>KC</t>
   </si>
   <si>
     <t>tackles for loss</t>
   </si>
   <si>
+    <t>LAC</t>
+  </si>
+  <si>
     <t>passes defended</t>
   </si>
   <si>
-    <t>KC</t>
+    <t>LAR</t>
   </si>
   <si>
     <t>interceptions caught</t>
   </si>
   <si>
-    <t>LAC</t>
+    <t>LV</t>
   </si>
   <si>
     <t>field goals</t>
   </si>
   <si>
-    <t>LAR</t>
+    <t>MIA</t>
   </si>
   <si>
     <t>kicking points</t>
   </si>
   <si>
-    <t>LV</t>
+    <t>MIN</t>
   </si>
   <si>
     <t>fumbles</t>
   </si>
   <si>
+    <t>NE</t>
+  </si>
+  <si>
     <t>fumbles lost</t>
   </si>
   <si>
-    <t>MIA</t>
-  </si>
-  <si>
-    <t>MIN</t>
+    <t>NO</t>
+  </si>
+  <si>
+    <t>NYG</t>
+  </si>
+  <si>
+    <t>points</t>
+  </si>
+  <si>
+    <t>NYJ</t>
+  </si>
+  <si>
+    <t>PHI</t>
+  </si>
+  <si>
+    <t>PIT</t>
+  </si>
+  <si>
+    <t>SEA</t>
+  </si>
+  <si>
+    <t>SF</t>
+  </si>
+  <si>
+    <t>TB</t>
+  </si>
+  <si>
+    <t>TEN</t>
+  </si>
+  <si>
+    <t>WSH</t>
+  </si>
+  <si>
+    <t>Rooting interests</t>
+  </si>
+  <si>
+    <t>Week</t>
   </si>
   <si>
     <t>Team stats</t>
   </si>
   <si>
-    <t>NE</t>
-  </si>
-  <si>
-    <t>points</t>
-  </si>
-  <si>
-    <t>NO</t>
-  </si>
-  <si>
-    <t>NYG</t>
-  </si>
-  <si>
-    <t>Rooting interests</t>
-  </si>
-  <si>
-    <t>NYJ</t>
-  </si>
-  <si>
-    <t>PHI</t>
-  </si>
-  <si>
-    <t>PIT</t>
-  </si>
-  <si>
-    <t>SEA</t>
-  </si>
-  <si>
-    <t>SF</t>
-  </si>
-  <si>
-    <t>TB</t>
-  </si>
-  <si>
-    <t>Week</t>
-  </si>
-  <si>
-    <t>TEN</t>
-  </si>
-  <si>
-    <t>WSH</t>
-  </si>
-  <si>
     <t>Fill the shaded cells. Leave Player blank for a team goal. Leave Direction and Target blank when the Stat is 'win' or 'any TD'.</t>
   </si>
   <si>
-    <t>Player</t>
-  </si>
-  <si>
-    <t>Target</t>
-  </si>
-  <si>
-    <t>James Cook</t>
-  </si>
-  <si>
-    <t>&lt;- example, overwrite or delete this row</t>
-  </si>
-  <si>
-    <t>Drake Maye</t>
-  </si>
-  <si>
-    <t>Christian Watson</t>
-  </si>
-  <si>
-    <t>JAC</t>
-  </si>
-  <si>
-    <t>-</t>
-  </si>
-  <si>
-    <t>Davanate Adams</t>
-  </si>
-  <si>
-    <t>Zay Flowers</t>
-  </si>
-  <si>
-    <t>Jonathan Taylor</t>
-  </si>
-  <si>
-    <t>rush + rec yds</t>
-  </si>
-  <si>
-    <t>Matthew Stafford</t>
-  </si>
-  <si>
-    <t>Hunter Henry</t>
-  </si>
-  <si>
-    <t>win by</t>
+    <t>Revised</t>
+  </si>
+  <si>
+    <t>BOZO?</t>
+  </si>
+  <si>
+    <t>Marvin Harrison 3+ Receptions</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>Trey McBride 6+ Receptions</t>
+  </si>
+  <si>
+    <t>Bijan Robinson Anytime TD</t>
+  </si>
+  <si>
+    <t>Christian McCaffrey Anytime TD</t>
+  </si>
+  <si>
+    <t>Derrick Henry 70+ Rushing Yds</t>
+  </si>
+  <si>
+    <t>Jaxon Smith-Njigba 7+ Receptions</t>
+  </si>
+  <si>
+    <t>Cincinnati Bengals Moneyline</t>
+  </si>
+  <si>
+    <t>Carolina Panthers Moneyline</t>
+  </si>
+  <si>
+    <t>San Francisco 49ers -2.5 Spread</t>
+  </si>
+  <si>
+    <t>Los Angeles Rams -3.5 Spread</t>
+  </si>
+  <si>
+    <t>Josh Jacobs Anytime TD</t>
+  </si>
+  <si>
+    <t>Kenneth Walker III Anytime TD</t>
+  </si>
+  <si>
+    <t>Brock Bowers 60+ Receiving Yds</t>
+  </si>
+  <si>
+    <t>C.J. Stroud 230+ Passing Yds</t>
+  </si>
+  <si>
+    <t>Jahmyr Gibbs 130+ Rushing + Receiving Yds</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="16">
+  <fonts count="18">
     <font>
       <sz val="11.0"/>
       <color theme="1"/>
@@ -316,14 +325,14 @@
     </font>
     <font>
       <b/>
-      <sz val="13.0"/>
-      <color rgb="FF1F2937"/>
+      <sz val="10.0"/>
+      <color theme="1"/>
       <name val="Arial"/>
     </font>
     <font>
       <b/>
-      <sz val="10.0"/>
-      <color theme="1"/>
+      <sz val="13.0"/>
+      <color rgb="FF1F2937"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -332,15 +341,15 @@
       <name val="Arial"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="10.0"/>
       <color rgb="FF1F2937"/>
       <name val="Arial"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -373,22 +382,31 @@
       <name val="Arial"/>
     </font>
     <font>
+      <b/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="&quot;Google Sans Text&quot;"/>
+    </font>
+    <font>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Google Sans Text"/>
+    </font>
+    <font>
+      <color rgb="FF1A1B1F"/>
+      <name val="Roboto"/>
     </font>
     <font>
       <color rgb="FF6B7280"/>
       <name val="Arial"/>
     </font>
     <font>
-      <i/>
-      <sz val="9.0"/>
-      <color rgb="FFB45309"/>
-      <name val="Arial"/>
-    </font>
-    <font>
-      <color rgb="FF1A1B1F"/>
-      <name val="Roboto"/>
+      <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <sz val="10.0"/>
@@ -396,7 +414,7 @@
       <name val="Arial"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -413,18 +431,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF1F2937"/>
         <bgColor rgb="FF1F2937"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF8F8FF"/>
-        <bgColor rgb="FFF8F8FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -459,7 +465,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="27">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -474,32 +480,51 @@
       <alignment horizontal="left" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="1" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="11" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="4" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="5" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="15" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="3" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="3" fillId="2" fontId="17" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
+    <xf borderId="3" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="17" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -534,7 +559,7 @@
     </dxf>
   </dxfs>
   <tableStyles count="1">
-    <tableStyle count="2" pivot="0" name="Rooting-style">
+    <tableStyle count="2" pivot="0" name="Rooting Revised-style">
       <tableStyleElement dxfId="1" type="firstRowStripe"/>
       <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
@@ -559,11 +584,11 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="K8:K13" displayName="Table_1" name="Table_1" id="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="H8:H13" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="1">
     <tableColumn name="Column1" id="1"/>
   </tableColumns>
-  <tableStyleInfo name="Rooting-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+  <tableStyleInfo name="Rooting Revised-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -768,25 +793,26 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="1" width="26.0"/>
-    <col customWidth="1" min="2" max="2" width="9.0"/>
-    <col customWidth="1" min="3" max="3" width="22.0"/>
-    <col customWidth="1" min="4" max="4" width="12.0"/>
-    <col customWidth="1" min="5" max="5" width="10.0"/>
-    <col customWidth="1" min="6" max="26" width="8.71"/>
+    <col customWidth="1" min="1" max="1" width="35.43"/>
+    <col customWidth="1" min="2" max="2" width="26.0"/>
+    <col customWidth="1" min="3" max="3" width="9.0"/>
+    <col customWidth="1" min="4" max="4" width="22.0"/>
+    <col customWidth="1" min="5" max="5" width="12.0"/>
+    <col customWidth="1" min="6" max="7" width="10.0"/>
+    <col customWidth="1" min="8" max="28" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="7" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B2" s="8">
-        <v>6.0</v>
+        <v>7.0</v>
       </c>
     </row>
     <row r="4">
@@ -798,436 +824,408 @@
       <c r="A6" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="10" t="s">
-        <v>1</v>
-      </c>
-      <c r="D6" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="E6" s="10" t="s">
+      <c r="C6" s="12" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="B7" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="D7" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E7" s="11">
-        <v>80.0</v>
-      </c>
-      <c r="F7" s="13" t="s">
+      <c r="B7" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="D8" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E8" s="11">
-        <v>210.0</v>
-      </c>
-      <c r="K8" s="14"/>
+      <c r="B8" s="14" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H8" s="16"/>
     </row>
     <row r="9">
-      <c r="A9" s="11"/>
-      <c r="B9" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D9" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E9" s="11">
-        <v>26.5</v>
-      </c>
-      <c r="K9" s="15"/>
+      <c r="A9" s="13" t="s">
+        <v>86</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="C9" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H9" s="16"/>
     </row>
     <row r="10">
-      <c r="A10" s="11" t="s">
-        <v>86</v>
-      </c>
-      <c r="B10" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C10" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E10" s="11">
-        <v>74.5</v>
-      </c>
-      <c r="K10" s="14"/>
+      <c r="A10" s="13" t="s">
+        <v>87</v>
+      </c>
+      <c r="B10" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C10" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H10" s="16"/>
     </row>
     <row r="11">
-      <c r="A11" s="11"/>
-      <c r="B11" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D11" s="11" t="s">
+      <c r="A11" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="E11" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="K11" s="15"/>
+      <c r="B11" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H11" s="16"/>
     </row>
     <row r="12">
-      <c r="A12" s="11" t="s">
+      <c r="A12" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="B12" s="11" t="s">
+      <c r="B12" s="14" t="s">
+        <v>72</v>
+      </c>
+      <c r="C12" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="H12" s="16"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F13" s="17"/>
+      <c r="H13" s="16"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="F14" s="17"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="B15" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>56</v>
+      </c>
+      <c r="C16" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="B17" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="B19" s="18" t="s">
         <v>58</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D12" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="11">
-        <v>1.0</v>
-      </c>
-      <c r="K12" s="14"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="11" t="s">
-        <v>90</v>
-      </c>
-      <c r="B13" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D13" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E13" s="11">
-        <v>5.0</v>
-      </c>
-      <c r="I13" s="12"/>
-      <c r="K13" s="15"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="B14" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="D14" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="11">
-        <v>90.0</v>
-      </c>
-      <c r="I14" s="12"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="11"/>
-      <c r="B15" s="11" t="s">
-        <v>69</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D15" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E15" s="11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="11"/>
-      <c r="B16" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D16" s="11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="B17" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E17" s="11">
-        <v>260.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="B18" s="11" t="s">
-        <v>66</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="D18" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" s="11">
-        <v>26.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D19" s="16" t="s">
-        <v>25</v>
-      </c>
-      <c r="E19" s="16">
-        <v>7.5</v>
-      </c>
+      <c r="C19" s="19"/>
     </row>
     <row r="20">
-      <c r="A20" s="17"/>
-      <c r="B20" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="D20" s="18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E20" s="11">
-        <v>3.0</v>
-      </c>
+      <c r="A20" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="B20" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="19"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="17"/>
-      <c r="B21" s="17"/>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="19"/>
+      <c r="A21" s="21" t="s">
+        <v>98</v>
+      </c>
+      <c r="B21" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="C21" s="23"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="23"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="25"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="17"/>
-      <c r="B22" s="17"/>
-      <c r="C22" s="17"/>
-      <c r="D22" s="17"/>
-      <c r="E22" s="19"/>
+      <c r="A22" s="26"/>
+      <c r="B22" s="23"/>
+      <c r="C22" s="23"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="23"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="25"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="17"/>
-      <c r="B23" s="17"/>
-      <c r="C23" s="17"/>
-      <c r="D23" s="17"/>
-      <c r="E23" s="19"/>
+      <c r="A23" s="26"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="23"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="23"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="25"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="17"/>
-      <c r="B24" s="17"/>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="19"/>
+      <c r="A24" s="26"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="23"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="23"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="25"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="17"/>
-      <c r="B25" s="17"/>
-      <c r="C25" s="17"/>
-      <c r="D25" s="17"/>
-      <c r="E25" s="19"/>
+      <c r="A25" s="26"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="23"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="23"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="25"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="17"/>
-      <c r="B26" s="17"/>
-      <c r="C26" s="17"/>
-      <c r="D26" s="17"/>
-      <c r="E26" s="19"/>
+      <c r="A26" s="26"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="23"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="23"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="25"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="17"/>
-      <c r="B27" s="17"/>
-      <c r="C27" s="17"/>
-      <c r="D27" s="17"/>
-      <c r="E27" s="19"/>
+      <c r="A27" s="26"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="23"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="23"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="25"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="17"/>
-      <c r="B28" s="17"/>
-      <c r="C28" s="17"/>
-      <c r="D28" s="17"/>
-      <c r="E28" s="19"/>
+      <c r="A28" s="26"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="23"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="23"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="25"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="17"/>
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="19"/>
+      <c r="A29" s="26"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="23"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="23"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="25"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="19"/>
+      <c r="A30" s="26"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="23"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="23"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="25"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="17"/>
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="19"/>
+      <c r="A31" s="26"/>
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="23"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="25"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="17"/>
-      <c r="B32" s="17"/>
-      <c r="C32" s="17"/>
-      <c r="D32" s="17"/>
-      <c r="E32" s="19"/>
+      <c r="A32" s="26"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="23"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="23"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="25"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="17"/>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17"/>
-      <c r="D33" s="17"/>
-      <c r="E33" s="19"/>
+      <c r="A33" s="26"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="23"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="23"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="25"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="17"/>
-      <c r="B34" s="17"/>
-      <c r="C34" s="17"/>
-      <c r="D34" s="17"/>
-      <c r="E34" s="19"/>
+      <c r="A34" s="26"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="23"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="25"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="17"/>
-      <c r="B35" s="17"/>
-      <c r="C35" s="17"/>
-      <c r="D35" s="17"/>
-      <c r="E35" s="19"/>
+      <c r="A35" s="26"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="23"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="25"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="17"/>
-      <c r="B36" s="17"/>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="19"/>
+      <c r="A36" s="26"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="23"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="25"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="17"/>
-      <c r="B37" s="17"/>
-      <c r="C37" s="17"/>
-      <c r="D37" s="17"/>
-      <c r="E37" s="19"/>
+      <c r="A37" s="26"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="23"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="25"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="17"/>
-      <c r="B38" s="17"/>
-      <c r="C38" s="17"/>
-      <c r="D38" s="17"/>
-      <c r="E38" s="19"/>
+      <c r="A38" s="26"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="23"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="25"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="17"/>
-      <c r="B39" s="17"/>
-      <c r="C39" s="17"/>
-      <c r="D39" s="17"/>
-      <c r="E39" s="19"/>
+      <c r="A39" s="26"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="23"/>
+      <c r="E39" s="23"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="25"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="17"/>
-      <c r="B40" s="17"/>
-      <c r="C40" s="17"/>
-      <c r="D40" s="17"/>
-      <c r="E40" s="19"/>
+      <c r="A40" s="26"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="D40" s="23"/>
+      <c r="E40" s="23"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="25"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="17"/>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="19"/>
+      <c r="A41" s="26"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
+      <c r="D41" s="23"/>
+      <c r="E41" s="23"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="25"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="19"/>
+      <c r="A42" s="26"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
+      <c r="D42" s="23"/>
+      <c r="E42" s="23"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="25"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="19"/>
+      <c r="A43" s="26"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="D43" s="23"/>
+      <c r="E43" s="23"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="25"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="17"/>
-      <c r="D44" s="17"/>
-      <c r="E44" s="19"/>
+      <c r="A44" s="26"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
+      <c r="D44" s="23"/>
+      <c r="E44" s="23"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="25"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="17"/>
-      <c r="D45" s="17"/>
-      <c r="E45" s="19"/>
+      <c r="A45" s="26"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="D45" s="23"/>
+      <c r="E45" s="23"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="25"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="17"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="17"/>
-      <c r="D46" s="17"/>
-      <c r="E46" s="19"/>
+      <c r="A46" s="26"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="23"/>
+      <c r="D46" s="23"/>
+      <c r="E46" s="23"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="25"/>
     </row>
     <row r="47" ht="15.75" customHeight="1"/>
     <row r="48" ht="15.75" customHeight="1"/>
@@ -2206,261 +2204,261 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="2" t="s">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B5" s="4" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="5" t="s">
+      <c r="C5" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C3" s="5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="5" t="s">
+      <c r="C6" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="C7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="5" t="s">
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="C8" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C5" s="5" t="s">
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="5" t="s">
+      <c r="C14" s="4" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="4" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="5" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C17" s="5" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="5" t="s">
-        <v>62</v>
-      </c>
-      <c r="C24" s="5" t="s">
+      <c r="C25" s="4" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="4" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C25" s="5" t="s">
+      <c r="C26" s="4" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C26" s="5" t="s">
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="C27" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="C28" s="4" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="C27" s="5" t="s">
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="C29" s="4" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="C28" s="5" t="s">
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="C30" s="4" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="C29" s="5" t="s">
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="C31" s="4" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="C30" s="5" t="s">
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="C32" s="4" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="C31" s="5" t="s">
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="C33" s="4" t="s">
         <v>76</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="C32" s="5" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="C33" s="5" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="34" ht="15.75" customHeight="1"/>
@@ -3451,8 +3449,8 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+      <c r="A1" s="2" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -3460,57 +3458,57 @@
       <c r="B3" s="3"/>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="s">
-        <v>4</v>
+      <c r="A4" s="5" t="s">
+        <v>9</v>
       </c>
       <c r="B4" s="3"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>8</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>13</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>17</v>
+        <v>37</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>21</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11">
@@ -3518,146 +3516,146 @@
       <c r="B11" s="3"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="s">
-        <v>23</v>
+      <c r="A12" s="5" t="s">
+        <v>45</v>
       </c>
       <c r="B12" s="3"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="B13" s="3"/>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="B14" s="3"/>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="B15" s="3"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="B16" s="3"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="B17" s="3"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>32</v>
+        <v>23</v>
       </c>
       <c r="B18" s="3"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="B19" s="3"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="B20" s="3"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="3" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="B21" s="3"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
       <c r="A22" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="B22" s="3"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="3" t="s">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="B23" s="3"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B24" s="3"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="3" t="s">
-        <v>12</v>
+        <v>29</v>
       </c>
       <c r="B25" s="3"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="3" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B26" s="3"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
       <c r="A27" s="3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B27" s="3"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="3" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B28" s="3"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B29" s="3"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
       <c r="A30" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="B30" s="3"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
       <c r="A31" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B31" s="3"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
       <c r="A32" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="B32" s="3"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B33" s="3"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
       <c r="A34" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B34" s="3"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
       <c r="B35" s="3"/>
     </row>
@@ -3666,20 +3664,20 @@
       <c r="B36" s="3"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="4" t="s">
-        <v>65</v>
+      <c r="A37" s="5" t="s">
+        <v>79</v>
       </c>
       <c r="B37" s="3"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="3" t="s">
-        <v>15</v>
+        <v>35</v>
       </c>
       <c r="B38" s="3"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="3" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B39" s="3"/>
     </row>
